--- a/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D62CF9-423A-4AEF-851B-0CA0D44E422C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31DE8AA3-EA9F-4194-8D4A-D9B1A60F9F12}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2041CD06-F98C-4AC4-B336-19F197C6763F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95FBBA3-3501-4942-B9C0-852934602468}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07641045-61FA-4196-A2E4-2C87B77113C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C501C397-926F-4F06-A048-D01349E78415}"/>
 </file>